--- a/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_104_Myanmar.xlsx
+++ b/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_104_Myanmar.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="Re33666c859694bd3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="R80c1a6d08fc44a91"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="Rb17e031b18dd425c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="Rae3c899695604ee4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="R127349df9f1b4f85"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="Rf0574ecb62ea4940"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="R14eee148ff394a32"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="R75eaccabcdb94c1e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="R616d929d7697482c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="Rcf81ce9bed284869"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="R7577c80c98c34813"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="R8ae713559ee8446b"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -18,13 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="6">
+  <x:numFmts count="4">
     <x:numFmt numFmtId="200" formatCode="0"/>
     <x:numFmt numFmtId="201" formatCode="#,##0.00"/>
     <x:numFmt numFmtId="202" formatCode="0.0000"/>
-    <x:numFmt numFmtId="203" formatCode="#,##0"/>
-    <x:numFmt numFmtId="204" formatCode="0.00%"/>
-    <x:numFmt numFmtId="205" formatCode="0.00"/>
+    <x:numFmt numFmtId="203" formatCode="0.00"/>
   </x:numFmts>
   <x:fonts count="7">
     <x:font>
@@ -184,7 +182,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="37">
+  <x:cellXfs count="35">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:extLst>
@@ -244,8 +242,6 @@
     <x:xf numFmtId="200" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="201" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="202" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="203" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="204" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <x:extLst>
         <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
@@ -253,14 +249,14 @@
         </x:ext>
       </x:extLst>
     </x:xf>
-    <x:xf numFmtId="205" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="203" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
-  <x:dxfs count="3">
+  <x:dxfs count="1">
     <x:dxf>
       <x:font>
         <x:color rgb="FF9A3412"/>
@@ -268,28 +264,6 @@
       <x:fill>
         <x:patternFill patternType="solid">
           <x:bgColor rgb="FFFCEAD8"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
@@ -345,56 +319,36 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ104CommercialTable" displayName="EEZ104CommercialTable" ref="A1:O11" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O11"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ104CommercialTable" displayName="EEZ104CommercialTable" ref="A1:E11" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E11"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="commercial_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ104FunctionalTable" displayName="EEZ104FunctionalTable" ref="A1:O20" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O20"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ104FunctionalTable" displayName="EEZ104FunctionalTable" ref="A1:E20" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E20"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="functional_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ104ValidationTable" displayName="EEZ104ValidationTable" ref="A1:D19" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:D19"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ104ValidationTable" displayName="EEZ104ValidationTable" ref="A1:D17" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:D17"/>
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="unit_id"/>
     <x:tableColumn id="2" name="check"/>
@@ -6121,7 +6075,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbc1501dad690429e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcadc8d58463f4901"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6131,20 +6085,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="26" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -6152,606 +6096,212 @@
         <x:v>commercial_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Anchovies</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>41179.7022503415</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>3.1999999999999997</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>158.48931924611125</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>41179.7022503415</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>158.48931924611142</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$H$2:$H$82,A2,'Species'!$U$2:$U$82))</x:f>
-        <x:v>6526542.976414187</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>3.1999999999999997</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>158.48931924611125</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>6526542.976414179</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>7.450580596923828e-9</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1.000000000000001</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>1.1415814810151352e-15</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Crustaceans</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>67646.75445076262</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>3.3822613977072176</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>241.13563643915992</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>67646.75445076262</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>261.18079435140993</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$H$2:$H$82,A3,'Species'!$U$2:$U$82))</x:f>
-        <x:v>17668033.062744956</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>3.3822613977072176</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>241.13563643915992</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>16312043.187528217</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>1355989.8752167393</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1.0831281440116278</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0.0831281440116279</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Flatfishes</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>3958.0456304902</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>4.39</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>2454.7089156850284</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>3958.0456304902</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>2454.7089156850284</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$H$2:$H$82,A4,'Species'!$U$2:$U$82))</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>9715849.897852464</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>4.39</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>2454.7089156850284</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
-        <x:v>9715849.897852464</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Herring-likes</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>101108.6879279575</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>3.344526299619275</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>221.0682124769484</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>101108.6879279575</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>452.73175897628164</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$H$2:$H$82,A5,'Species'!$U$2:$U$82))</x:f>
-        <x:v>45775114.13340813</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>3.344526299619275</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>221.0682124769484</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>22351916.906123172</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>23423197.227284957</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>2.047927894760038</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>1.047927894760038</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Molluscs</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>944.193114489</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>2.1</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>12.589254117941675</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>944.193114489</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>12.589254117941675</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$H$2:$H$82,A6,'Species'!$U$2:$U$82))</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>11886.687054712818</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>2.1</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>12.589254117941675</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
-        <x:v>11886.687054712818</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Other fishes &amp; inverts</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>632764.6121292852</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>3.407046702402432</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>255.29758253614273</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>632764.6121292852</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>322.3893493530029</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$H$2:$H$82,A7,'Species'!$U$2:$U$82))</x:f>
-        <x:v>203996571.5979655</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>3.407046702402432</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>255.29758253614273</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>161543275.79102653</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>42453295.806938976</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.2627982848500414</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0.2627982848500413</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Perch-likes</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>425467.6478529367</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>3.731359863392143</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>538.7159863549853</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>425467.6478529367</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>815.7705197410395</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$H$2:$H$82,A8,'Species'!$U$2:$U$82))</x:f>
-        <x:v>347083964.2219877</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>3.731359863392143</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>538.7159863549853</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>229206223.57523033</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>117877740.6467574</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1.514286823490495</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0.5142868234904949</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Scorpionfishes</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>1427.0050507493</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>3.9</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>794.3282347242813</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>1427.0050507493</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>794.3282347242814</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$H$2:$H$82,A9,'Species'!$U$2:$U$82))</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>1133510.402904325</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>3.9</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>794.3282347242813</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
-        <x:v>1133510.402904325</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Sharks &amp; rays</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>46574.4813220033</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>4.0496681698055585</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>1121.1614841699973</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>46574.4813220033</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>1121.4179614128932</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$H$2:$H$82,A10,'Species'!$U$2:$U$82))</x:f>
-        <x:v>52229459.89798382</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>4.0496681698055585</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>1121.1614841699973</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>52217514.60342504</x:v>
-      </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>11945.294558778405</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1.000228760304842</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>0.00022876030484213992</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="18" customHeight="1">
       <x:c r="A11" s="24" t="str">
         <x:v>Tuna &amp; billfishes</x:v>
       </x:c>
-      <x:c r="B11" s="33" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="D11" s="31" t="n">
+      <x:c r="B11" s="31" t="n">
         <x:v>12863.7695078624</x:v>
       </x:c>
+      <x:c r="C11" s="32" t="n">
+        <x:v>4.432932392367037</x:v>
+      </x:c>
+      <x:c r="D11" s="32" t="n">
+        <x:f>IF(C11="","",(1/'Metadata'!$B$5)^(C11-1))</x:f>
+        <x:v>2709.7697628881474</x:v>
+      </x:c>
       <x:c r="E11" s="31" t="n">
-        <x:v>12863.7695078624</x:v>
-      </x:c>
-      <x:c r="F11" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H11" s="32" t="n">
-        <x:f>IF(E11=0,"",I11/E11)</x:f>
-        <x:v>2775.658977974046</x:v>
-      </x:c>
-      <x:c r="I11" s="31" t="n">
-        <x:f>IF(C11=0,"",SUMIF('Species'!$H$2:$H$82,A11,'Species'!$U$2:$U$82))</x:f>
-        <x:v>35705437.32508705</x:v>
-      </x:c>
-      <x:c r="J11" s="32" t="n">
-        <x:v>4.432932392367037</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:f>IF(J11="","",(1/'Metadata'!$B$5)^(J11-1))</x:f>
-        <x:v>2709.7697628881474</x:v>
-      </x:c>
-      <x:c r="L11" s="31" t="n">
-        <x:f>IF(E11=0,"",E11*K11)</x:f>
+        <x:f>IF(B11=0,"",B11*D11)</x:f>
         <x:v>34857853.649168074</x:v>
       </x:c>
-      <x:c r="M11" s="31" t="n">
-        <x:f>IF(E11=0,"",I11-L11)</x:f>
-        <x:v>847583.675918974</x:v>
-      </x:c>
-      <x:c r="N11" s="32" t="n">
-        <x:f>IF(L11=0,"",I11/L11)</x:f>
-        <x:v>1.0243154292989352</x:v>
-      </x:c>
-      <x:c r="O11" s="34" t="n">
-        <x:f>IF(L11=0,"",M11/L11)</x:f>
-        <x:v>0.024315429298935123</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G11">
-    <x:cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O11">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3a38187d278740fc"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1964a4869c6846cc"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6761,20 +6311,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="34" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -6782,1092 +6322,383 @@
         <x:v>functional_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Cephalopods</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>42168.07022604319</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>3.81264931090511</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>649.6049280548863</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>42168.07022604319</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>651.0946267087862</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$G$2:$G$82,A2,'Species'!$U$2:$U$82))</x:f>
-        <x:v>27455403.942855477</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>3.81264931090511</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>649.6049280548863</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>27392586.22540218</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>62817.71745329723</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1.0022932379197933</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0.0022932379197932026</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Jellyfish</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>2793.7556410028</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>3.46</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>288.40315031266056</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>2793.7556410028</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>288.40315031266056</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$G$2:$G$82,A3,'Species'!$U$2:$U$82))</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>805727.9280689739</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>3.46</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>288.40315031266056</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
-        <x:v>805727.9280689739</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Large benthopelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>20964.129830877497</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>4.1532257044193654</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>1423.068168671605</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>20964.129830877497</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>1426.4967981754655</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$G$2:$G$82,A4,'Species'!$U$2:$U$82))</x:f>
-        <x:v>29905264.08028151</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>4.1532257044193654</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>1423.068168671605</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>29833385.846220605</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>71878.23406090587</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1.002409322040462</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0.002409322040461983</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Large demersals (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>58263.330822259304</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>3.8903581238800644</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>776.88748230278</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>58263.330822259304</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>777.4144137621482</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$G$2:$G$82,A5,'Species'!$U$2:$U$82))</x:f>
-        <x:v>45294753.17501682</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>3.8903581238800644</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>776.88748230278</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>45264052.39307899</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>30700.78193783015</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1.000678259685439</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0.0006782596854391321</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Large pelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>44782.593152845104</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>4.368456969069031</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>2335.914642769628</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>44782.593152845104</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>2374.5964155085117</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$G$2:$G$82,A6,'Species'!$U$2:$U$82))</x:f>
-        <x:v>106340585.177922</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>4.368456969069031</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>2335.914642769628</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>104608315.08692575</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>1732270.0909962505</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1.0165595831417111</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0.016559583141711024</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Large rays (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>46.8280421976</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>3.719966574134631</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>524.7670695259991</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>46.8280421976</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>524.777067870401</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$G$2:$G$82,A7,'Species'!$U$2:$U$82))</x:f>
-        <x:v>24574.282678567935</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>3.719966574134631</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>524.7670695259991</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>24573.81447567438</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>0.46820289355673594</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.000019052918871</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0.000019052918871028755</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Large sharks (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>46527.6532798057</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>4.05</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>1122.018454301963</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>46527.6532798057</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>1122.018454301963</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$G$2:$G$82,A8,'Species'!$U$2:$U$82))</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>52204885.61530525</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>4.05</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>1122.018454301963</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
-        <x:v>52204885.61530525</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Lobsters, crabs</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>32006.156864872897</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>3.489699989744797</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>308.8161396262283</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>32006.156864872897</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>333.9651802069526</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$G$2:$G$82,A9,'Species'!$U$2:$U$82))</x:f>
-        <x:v>10688941.94510927</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>3.489699989744797</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>308.8161396262283</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>9884017.807281554</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>804924.1378277168</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1.0814369372376818</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0.08143693723768176</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Medium benthopelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>31159.957729088</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>3.158003655872975</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>143.88106900537093</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>31159.957729088</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>155.61772757045009</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$G$2:$G$82,A10,'Species'!$U$2:$U$82))</x:f>
-        <x:v>4849041.812991957</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>3.158003655872975</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>143.88106900537093</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>4483328.028223352</x:v>
-      </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>365713.7847686056</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1.0815719444275262</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>0.08157194442752615</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="18" customHeight="1">
       <x:c r="A11" s="24" t="str">
         <x:v>Medium demersals (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B11" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D11" s="31" t="n">
+      <x:c r="B11" s="31" t="n">
         <x:v>609658.0396156724</x:v>
       </x:c>
+      <x:c r="C11" s="32" t="n">
+        <x:v>3.381136108869556</x:v>
+      </x:c>
+      <x:c r="D11" s="32" t="n">
+        <x:f>IF(C11="","",(1/'Metadata'!$B$5)^(C11-1))</x:f>
+        <x:v>240.5116450819807</x:v>
+      </x:c>
       <x:c r="E11" s="31" t="n">
-        <x:v>609658.0396156724</x:v>
-      </x:c>
-      <x:c r="F11" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H11" s="32" t="n">
-        <x:f>IF(E11=0,"",I11/E11)</x:f>
-        <x:v>291.88755954014607</x:v>
-      </x:c>
-      <x:c r="I11" s="31" t="n">
-        <x:f>IF(C11=0,"",SUMIF('Species'!$G$2:$G$82,A11,'Species'!$U$2:$U$82))</x:f>
-        <x:v>177951597.33744833</x:v>
-      </x:c>
-      <x:c r="J11" s="32" t="n">
-        <x:v>3.381136108869556</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:f>IF(J11="","",(1/'Metadata'!$B$5)^(J11-1))</x:f>
-        <x:v>240.5116450819807</x:v>
-      </x:c>
-      <x:c r="L11" s="31" t="n">
-        <x:f>IF(E11=0,"",E11*K11)</x:f>
+        <x:f>IF(B11=0,"",B11*D11)</x:f>
         <x:v>146629858.04542074</x:v>
-      </x:c>
-      <x:c r="M11" s="31" t="n">
-        <x:f>IF(E11=0,"",I11-L11)</x:f>
-        <x:v>31321739.292027593</x:v>
-      </x:c>
-      <x:c r="N11" s="32" t="n">
-        <x:f>IF(L11=0,"",I11/L11)</x:f>
-        <x:v>1.213610922833501</x:v>
-      </x:c>
-      <x:c r="O11" s="34" t="n">
-        <x:f>IF(L11=0,"",M11/L11)</x:f>
-        <x:v>0.2136109228335011</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="18" customHeight="1">
       <x:c r="A12" s="24" t="str">
         <x:v>Medium pelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B12" s="33" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="C12" s="33" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="D12" s="31" t="n">
+      <x:c r="B12" s="31" t="n">
         <x:v>165375.6401611356</x:v>
       </x:c>
+      <x:c r="C12" s="32" t="n">
+        <x:v>3.8680029241538976</x:v>
+      </x:c>
+      <x:c r="D12" s="32" t="n">
+        <x:f>IF(C12="","",(1/'Metadata'!$B$5)^(C12-1))</x:f>
+        <x:v>737.9091985385205</x:v>
+      </x:c>
       <x:c r="E12" s="31" t="n">
-        <x:v>165375.6401611356</x:v>
-      </x:c>
-      <x:c r="F12" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G12" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H12" s="32" t="n">
-        <x:f>IF(E12=0,"",I12/E12)</x:f>
-        <x:v>1012.9399925232585</x:v>
-      </x:c>
-      <x:c r="I12" s="31" t="n">
-        <x:f>IF(C12=0,"",SUMIF('Species'!$G$2:$G$82,A12,'Species'!$U$2:$U$82))</x:f>
-        <x:v>167515599.7083498</x:v>
-      </x:c>
-      <x:c r="J12" s="32" t="n">
-        <x:v>3.8680029241538976</x:v>
-      </x:c>
-      <x:c r="K12" s="32" t="n">
-        <x:f>IF(J12="","",(1/'Metadata'!$B$5)^(J12-1))</x:f>
-        <x:v>737.9091985385205</x:v>
-      </x:c>
-      <x:c r="L12" s="31" t="n">
-        <x:f>IF(E12=0,"",E12*K12)</x:f>
+        <x:f>IF(B12=0,"",B12*D12)</x:f>
         <x:v>122032206.08909835</x:v>
-      </x:c>
-      <x:c r="M12" s="31" t="n">
-        <x:f>IF(E12=0,"",I12-L12)</x:f>
-        <x:v>45483393.619251445</x:v>
-      </x:c>
-      <x:c r="N12" s="32" t="n">
-        <x:f>IF(L12=0,"",I12/L12)</x:f>
-        <x:v>1.3727163105290667</x:v>
-      </x:c>
-      <x:c r="O12" s="34" t="n">
-        <x:f>IF(L12=0,"",M12/L12)</x:f>
-        <x:v>0.37271631052906673</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="18" customHeight="1">
       <x:c r="A13" s="24" t="str">
         <x:v>Medium reef assoc. fish (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B13" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C13" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D13" s="31" t="n">
+      <x:c r="B13" s="31" t="n">
         <x:v>42416.42689462269</x:v>
       </x:c>
+      <x:c r="C13" s="32" t="n">
+        <x:v>3.478657137871491</x:v>
+      </x:c>
+      <x:c r="D13" s="32" t="n">
+        <x:f>IF(C13="","",(1/'Metadata'!$B$5)^(C13-1))</x:f>
+        <x:v>301.0628287350626</x:v>
+      </x:c>
       <x:c r="E13" s="31" t="n">
-        <x:v>42416.42689462269</x:v>
-      </x:c>
-      <x:c r="F13" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G13" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H13" s="32" t="n">
-        <x:f>IF(E13=0,"",I13/E13)</x:f>
-        <x:v>892.9263072937075</x:v>
-      </x:c>
-      <x:c r="I13" s="31" t="n">
-        <x:f>IF(C13=0,"",SUMIF('Species'!$G$2:$G$82,A13,'Species'!$U$2:$U$82))</x:f>
-        <x:v>37874743.43560894</x:v>
-      </x:c>
-      <x:c r="J13" s="32" t="n">
-        <x:v>3.478657137871491</x:v>
-      </x:c>
-      <x:c r="K13" s="32" t="n">
-        <x:f>IF(J13="","",(1/'Metadata'!$B$5)^(J13-1))</x:f>
-        <x:v>301.0628287350626</x:v>
-      </x:c>
-      <x:c r="L13" s="31" t="n">
-        <x:f>IF(E13=0,"",E13*K13)</x:f>
+        <x:f>IF(B13=0,"",B13*D13)</x:f>
         <x:v>12770009.465729095</x:v>
-      </x:c>
-      <x:c r="M13" s="31" t="n">
-        <x:f>IF(E13=0,"",I13-L13)</x:f>
-        <x:v>25104733.969879843</x:v>
-      </x:c>
-      <x:c r="N13" s="32" t="n">
-        <x:f>IF(L13=0,"",I13/L13)</x:f>
-        <x:v>2.965913497343403</x:v>
-      </x:c>
-      <x:c r="O13" s="34" t="n">
-        <x:f>IF(L13=0,"",M13/L13)</x:f>
-        <x:v>1.9659134973434027</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="18" customHeight="1">
       <x:c r="A14" s="24" t="str">
         <x:v>Other demersal invertebrates</x:v>
       </x:c>
-      <x:c r="B14" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C14" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D14" s="31" t="n">
+      <x:c r="B14" s="31" t="n">
         <x:v>1007.0995621976</x:v>
       </x:c>
+      <x:c r="C14" s="32" t="n">
+        <x:v>2.1206127859876527</x:v>
+      </x:c>
+      <x:c r="D14" s="32" t="n">
+        <x:f>IF(C14="","",(1/'Metadata'!$B$5)^(C14-1))</x:f>
+        <x:v>13.20118100985568</x:v>
+      </x:c>
       <x:c r="E14" s="31" t="n">
-        <x:v>1007.0995621976</x:v>
-      </x:c>
-      <x:c r="F14" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G14" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H14" s="32" t="n">
-        <x:f>IF(E14=0,"",I14/E14)</x:f>
-        <x:v>13.48410474836391</x:v>
-      </x:c>
-      <x:c r="I14" s="31" t="n">
-        <x:f>IF(C14=0,"",SUMIF('Species'!$G$2:$G$82,A14,'Species'!$U$2:$U$82))</x:f>
-        <x:v>13579.835988703873</x:v>
-      </x:c>
-      <x:c r="J14" s="32" t="n">
-        <x:v>2.1206127859876527</x:v>
-      </x:c>
-      <x:c r="K14" s="32" t="n">
-        <x:f>IF(J14="","",(1/'Metadata'!$B$5)^(J14-1))</x:f>
-        <x:v>13.20118100985568</x:v>
-      </x:c>
-      <x:c r="L14" s="31" t="n">
-        <x:f>IF(E14=0,"",E14*K14)</x:f>
+        <x:f>IF(B14=0,"",B14*D14)</x:f>
         <x:v>13294.903615516927</x:v>
-      </x:c>
-      <x:c r="M14" s="31" t="n">
-        <x:f>IF(E14=0,"",I14-L14)</x:f>
-        <x:v>284.9323731869463</x:v>
-      </x:c>
-      <x:c r="N14" s="32" t="n">
-        <x:f>IF(L14=0,"",I14/L14)</x:f>
-        <x:v>1.0214316990500323</x:v>
-      </x:c>
-      <x:c r="O14" s="34" t="n">
-        <x:f>IF(L14=0,"",M14/L14)</x:f>
-        <x:v>0.021431699050032386</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="18" customHeight="1">
       <x:c r="A15" s="24" t="str">
         <x:v>Shrimps</x:v>
       </x:c>
-      <x:c r="B15" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="C15" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="D15" s="31" t="n">
+      <x:c r="B15" s="31" t="n">
         <x:v>35640.59758588971</x:v>
       </x:c>
+      <x:c r="C15" s="32" t="n">
+        <x:v>3.285778828305596</x:v>
+      </x:c>
+      <x:c r="D15" s="32" t="n">
+        <x:f>IF(C15="","",(1/'Metadata'!$B$5)^(C15-1))</x:f>
+        <x:v>193.0984680478821</x:v>
+      </x:c>
       <x:c r="E15" s="31" t="n">
-        <x:v>35640.59758588971</x:v>
-      </x:c>
-      <x:c r="F15" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G15" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H15" s="32" t="n">
-        <x:f>IF(E15=0,"",I15/E15)</x:f>
-        <x:v>195.81857741910426</x:v>
-      </x:c>
-      <x:c r="I15" s="31" t="n">
-        <x:f>IF(C15=0,"",SUMIF('Species'!$G$2:$G$82,A15,'Species'!$U$2:$U$82))</x:f>
-        <x:v>6979091.117635684</x:v>
-      </x:c>
-      <x:c r="J15" s="32" t="n">
-        <x:v>3.285778828305596</x:v>
-      </x:c>
-      <x:c r="K15" s="32" t="n">
-        <x:f>IF(J15="","",(1/'Metadata'!$B$5)^(J15-1))</x:f>
-        <x:v>193.0984680478821</x:v>
-      </x:c>
-      <x:c r="L15" s="31" t="n">
-        <x:f>IF(E15=0,"",E15*K15)</x:f>
+        <x:f>IF(B15=0,"",B15*D15)</x:f>
         <x:v>6882144.794146348</x:v>
-      </x:c>
-      <x:c r="M15" s="31" t="n">
-        <x:f>IF(E15=0,"",I15-L15)</x:f>
-        <x:v>96946.3234893363</x:v>
-      </x:c>
-      <x:c r="N15" s="32" t="n">
-        <x:f>IF(L15=0,"",I15/L15)</x:f>
-        <x:v>1.0140866439735174</x:v>
-      </x:c>
-      <x:c r="O15" s="34" t="n">
-        <x:f>IF(L15=0,"",M15/L15)</x:f>
-        <x:v>0.014086643973517473</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="18" customHeight="1">
       <x:c r="A16" s="24" t="str">
         <x:v>Small benthopelagics (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B16" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C16" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D16" s="31" t="n">
+      <x:c r="B16" s="31" t="n">
         <x:v>6786.6552484896</x:v>
       </x:c>
+      <x:c r="C16" s="32" t="n">
+        <x:v>3.24</x:v>
+      </x:c>
+      <x:c r="D16" s="32" t="n">
+        <x:f>IF(C16="","",(1/'Metadata'!$B$5)^(C16-1))</x:f>
+        <x:v>173.78008287493762</x:v>
+      </x:c>
       <x:c r="E16" s="31" t="n">
-        <x:v>6786.6552484896</x:v>
-      </x:c>
-      <x:c r="F16" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G16" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H16" s="32" t="n">
-        <x:f>IF(E16=0,"",I16/E16)</x:f>
-        <x:v>173.7800828749376</x:v>
-      </x:c>
-      <x:c r="I16" s="31" t="n">
-        <x:f>IF(C16=0,"",SUMIF('Species'!$G$2:$G$82,A16,'Species'!$U$2:$U$82))</x:f>
+        <x:f>IF(B16=0,"",B16*D16)</x:f>
         <x:v>1179385.511526153</x:v>
-      </x:c>
-      <x:c r="J16" s="32" t="n">
-        <x:v>3.24</x:v>
-      </x:c>
-      <x:c r="K16" s="32" t="n">
-        <x:f>IF(J16="","",(1/'Metadata'!$B$5)^(J16-1))</x:f>
-        <x:v>173.78008287493762</x:v>
-      </x:c>
-      <x:c r="L16" s="31" t="n">
-        <x:f>IF(E16=0,"",E16*K16)</x:f>
-        <x:v>1179385.511526153</x:v>
-      </x:c>
-      <x:c r="M16" s="31" t="n">
-        <x:f>IF(E16=0,"",I16-L16)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N16" s="32" t="n">
-        <x:f>IF(L16=0,"",I16/L16)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O16" s="34" t="n">
-        <x:f>IF(L16=0,"",M16/L16)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="18" customHeight="1">
       <x:c r="A17" s="24" t="str">
         <x:v>Small demersals (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B17" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C17" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D17" s="31" t="n">
+      <x:c r="B17" s="31" t="n">
         <x:v>64714.8009888808</x:v>
       </x:c>
+      <x:c r="C17" s="32" t="n">
+        <x:v>3.5372277548005417</x:v>
+      </x:c>
+      <x:c r="D17" s="32" t="n">
+        <x:f>IF(C17="","",(1/'Metadata'!$B$5)^(C17-1))</x:f>
+        <x:v>344.5305637699405</x:v>
+      </x:c>
       <x:c r="E17" s="31" t="n">
-        <x:v>64714.8009888808</x:v>
-      </x:c>
-      <x:c r="F17" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G17" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H17" s="32" t="n">
-        <x:f>IF(E17=0,"",I17/E17)</x:f>
-        <x:v>346.6817352122898</x:v>
-      </x:c>
-      <x:c r="I17" s="31" t="n">
-        <x:f>IF(C17=0,"",SUMIF('Species'!$G$2:$G$82,A17,'Species'!$U$2:$U$82))</x:f>
-        <x:v>22435439.500743207</x:v>
-      </x:c>
-      <x:c r="J17" s="32" t="n">
-        <x:v>3.5372277548005417</x:v>
-      </x:c>
-      <x:c r="K17" s="32" t="n">
-        <x:f>IF(J17="","",(1/'Metadata'!$B$5)^(J17-1))</x:f>
-        <x:v>344.5305637699405</x:v>
-      </x:c>
-      <x:c r="L17" s="31" t="n">
-        <x:f>IF(E17=0,"",E17*K17)</x:f>
+        <x:f>IF(B17=0,"",B17*D17)</x:f>
         <x:v>22296226.868958604</x:v>
-      </x:c>
-      <x:c r="M17" s="31" t="n">
-        <x:f>IF(E17=0,"",I17-L17)</x:f>
-        <x:v>139212.631784603</x:v>
-      </x:c>
-      <x:c r="N17" s="32" t="n">
-        <x:f>IF(L17=0,"",I17/L17)</x:f>
-        <x:v>1.0062437753527893</x:v>
-      </x:c>
-      <x:c r="O17" s="34" t="n">
-        <x:f>IF(L17=0,"",M17/L17)</x:f>
-        <x:v>0.0062437753527893325</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="18" customHeight="1">
       <x:c r="A18" s="24" t="str">
         <x:v>Small pelagics (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B18" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C18" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D18" s="31" t="n">
+      <x:c r="B18" s="31" t="n">
         <x:v>125321.3558176567</x:v>
       </x:c>
+      <x:c r="C18" s="32" t="n">
+        <x:v>3.167861505688897</x:v>
+      </x:c>
+      <x:c r="D18" s="32" t="n">
+        <x:f>IF(C18="","",(1/'Metadata'!$B$5)^(C18-1))</x:f>
+        <x:v>147.18430642858755</x:v>
+      </x:c>
       <x:c r="E18" s="31" t="n">
-        <x:v>125321.3558176567</x:v>
-      </x:c>
-      <x:c r="F18" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G18" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H18" s="32" t="n">
-        <x:f>IF(E18=0,"",I18/E18)</x:f>
-        <x:v>147.9661324451845</x:v>
-      </x:c>
-      <x:c r="I18" s="31" t="n">
-        <x:f>IF(C18=0,"",SUMIF('Species'!$G$2:$G$82,A18,'Species'!$U$2:$U$82))</x:f>
-        <x:v>18543316.333125487</x:v>
-      </x:c>
-      <x:c r="J18" s="32" t="n">
-        <x:v>3.167861505688897</x:v>
-      </x:c>
-      <x:c r="K18" s="32" t="n">
-        <x:f>IF(J18="","",(1/'Metadata'!$B$5)^(J18-1))</x:f>
-        <x:v>147.18430642858755</x:v>
-      </x:c>
-      <x:c r="L18" s="31" t="n">
-        <x:f>IF(E18=0,"",E18*K18)</x:f>
+        <x:f>IF(B18=0,"",B18*D18)</x:f>
         <x:v>18445336.836712036</x:v>
-      </x:c>
-      <x:c r="M18" s="31" t="n">
-        <x:f>IF(E18=0,"",I18-L18)</x:f>
-        <x:v>97979.49641345069</x:v>
-      </x:c>
-      <x:c r="N18" s="32" t="n">
-        <x:f>IF(L18=0,"",I18/L18)</x:f>
-        <x:v>1.005311884368435</x:v>
-      </x:c>
-      <x:c r="O18" s="34" t="n">
-        <x:f>IF(L18=0,"",M18/L18)</x:f>
-        <x:v>0.005311884368435094</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="18" customHeight="1">
       <x:c r="A19" s="24" t="str">
         <x:v>Small reef assoc. fish (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B19" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C19" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D19" s="31" t="n">
+      <x:c r="B19" s="31" t="n">
         <x:v>343.7621428502</x:v>
       </x:c>
+      <x:c r="C19" s="32" t="n">
+        <x:v>3.3</x:v>
+      </x:c>
+      <x:c r="D19" s="32" t="n">
+        <x:f>IF(C19="","",(1/'Metadata'!$B$5)^(C19-1))</x:f>
+        <x:v>199.52623149688787</x:v>
+      </x:c>
       <x:c r="E19" s="31" t="n">
-        <x:v>343.7621428502</x:v>
-      </x:c>
-      <x:c r="F19" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G19" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H19" s="32" t="n">
-        <x:f>IF(E19=0,"",I19/E19)</x:f>
-        <x:v>199.52623149688785</x:v>
-      </x:c>
-      <x:c r="I19" s="31" t="n">
-        <x:f>IF(C19=0,"",SUMIF('Species'!$G$2:$G$82,A19,'Species'!$U$2:$U$82))</x:f>
+        <x:f>IF(B19=0,"",B19*D19)</x:f>
         <x:v>68589.56489419524</x:v>
-      </x:c>
-      <x:c r="J19" s="32" t="n">
-        <x:v>3.3</x:v>
-      </x:c>
-      <x:c r="K19" s="32" t="n">
-        <x:f>IF(J19="","",(1/'Metadata'!$B$5)^(J19-1))</x:f>
-        <x:v>199.52623149688787</x:v>
-      </x:c>
-      <x:c r="L19" s="31" t="n">
-        <x:f>IF(E19=0,"",E19*K19)</x:f>
-        <x:v>68589.56489419524</x:v>
-      </x:c>
-      <x:c r="M19" s="31" t="n">
-        <x:f>IF(E19=0,"",I19-L19)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N19" s="32" t="n">
-        <x:f>IF(L19=0,"",I19/L19)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O19" s="34" t="n">
-        <x:f>IF(L19=0,"",M19/L19)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="18" customHeight="1">
       <x:c r="A20" s="24" t="str">
         <x:v>Small to medium flatfishes (&lt;90 cm)</x:v>
       </x:c>
-      <x:c r="B20" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C20" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D20" s="31" t="n">
+      <x:c r="B20" s="31" t="n">
         <x:v>3958.0456304902</x:v>
       </x:c>
+      <x:c r="C20" s="32" t="n">
+        <x:v>4.39</x:v>
+      </x:c>
+      <x:c r="D20" s="32" t="n">
+        <x:f>IF(C20="","",(1/'Metadata'!$B$5)^(C20-1))</x:f>
+        <x:v>2454.7089156850284</x:v>
+      </x:c>
       <x:c r="E20" s="31" t="n">
-        <x:v>3958.0456304902</x:v>
-      </x:c>
-      <x:c r="F20" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G20" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H20" s="32" t="n">
-        <x:f>IF(E20=0,"",I20/E20)</x:f>
-        <x:v>2454.7089156850284</x:v>
-      </x:c>
-      <x:c r="I20" s="31" t="n">
-        <x:f>IF(C20=0,"",SUMIF('Species'!$G$2:$G$82,A20,'Species'!$U$2:$U$82))</x:f>
+        <x:f>IF(B20=0,"",B20*D20)</x:f>
         <x:v>9715849.897852464</x:v>
       </x:c>
-      <x:c r="J20" s="32" t="n">
-        <x:v>4.39</x:v>
-      </x:c>
-      <x:c r="K20" s="32" t="n">
-        <x:f>IF(J20="","",(1/'Metadata'!$B$5)^(J20-1))</x:f>
-        <x:v>2454.7089156850284</x:v>
-      </x:c>
-      <x:c r="L20" s="31" t="n">
-        <x:f>IF(E20=0,"",E20*K20)</x:f>
-        <x:v>9715849.897852464</x:v>
-      </x:c>
-      <x:c r="M20" s="31" t="n">
-        <x:f>IF(E20=0,"",I20-L20)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N20" s="32" t="n">
-        <x:f>IF(L20=0,"",I20/L20)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O20" s="34" t="n">
-        <x:f>IF(L20=0,"",M20/L20)</x:f>
-        <x:v>0</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G20">
-    <x:cfRule type="cellIs" dxfId="2" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O20">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R414f3e11d0314407"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re77c93786e1443a9"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8042,7 +6873,7 @@
       <x:c r="B5" s="24" t="str">
         <x:v>catch_reconciled</x:v>
       </x:c>
-      <x:c r="C5" s="35" t="b">
+      <x:c r="C5" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D5" s="24" t="str">
@@ -8141,7 +6972,7 @@
         <x:v>commercial_ppr</x:v>
       </x:c>
       <x:c r="C12" s="24" t="n">
-        <x:v>719846370.2034028</x:v>
+        <x:v>533876617.67672706</x:v>
       </x:c>
       <x:c r="D12" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -8155,7 +6986,7 @@
         <x:v>functional_ppr</x:v>
       </x:c>
       <x:c r="C13" s="24" t="n">
-        <x:v>719846370.2034026</x:v>
+        <x:v>614533774.7229358</x:v>
       </x:c>
       <x:c r="D13" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -8169,7 +7000,7 @@
         <x:v>commercial_ppr_difference</x:v>
       </x:c>
       <x:c r="C14" s="24" t="n">
-        <x:v>-1.1920928955078125e-7</x:v>
+        <x:v>-185969752.52667582</x:v>
       </x:c>
       <x:c r="D14" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -8183,7 +7014,7 @@
         <x:v>functional_ppr_difference</x:v>
       </x:c>
       <x:c r="C15" s="24" t="n">
-        <x:v>-2.384185791015625e-7</x:v>
+        <x:v>-105312595.48046708</x:v>
       </x:c>
       <x:c r="D15" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -8194,9 +7025,9 @@
         <x:v>EEZ_104</x:v>
       </x:c>
       <x:c r="B16" s="24" t="str">
-        <x:v>commercial_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C16" s="35" t="b">
+        <x:v>tl_coverage_complete</x:v>
+      </x:c>
+      <x:c r="C16" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D16" s="24" t="str">
@@ -8208,47 +7039,19 @@
         <x:v>EEZ_104</x:v>
       </x:c>
       <x:c r="B17" s="24" t="str">
-        <x:v>functional_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C17" s="35" t="b">
+        <x:v>group_ppr_within_convexity_bound</x:v>
+      </x:c>
+      <x:c r="C17" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D17" s="24" t="str">
         <x:v>boolean</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" ht="18" customHeight="1">
-      <x:c r="A18" s="24" t="str">
-        <x:v>EEZ_104</x:v>
-      </x:c>
-      <x:c r="B18" s="24" t="str">
-        <x:v>commercial_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C18" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D18" s="24" t="str">
-        <x:v>count</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" ht="18" customHeight="1">
-      <x:c r="A19" s="24" t="str">
-        <x:v>EEZ_104</x:v>
-      </x:c>
-      <x:c r="B19" s="24" t="str">
-        <x:v>functional_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C19" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D19" s="24" t="str">
-        <x:v>count</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9c7757fd0c2f4c15"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3c5a8b70ef974750"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8295,7 +7098,7 @@
       <x:c r="A5" s="22" t="str">
         <x:v>Transfer efficiency</x:v>
       </x:c>
-      <x:c r="B5" s="36" t="n">
+      <x:c r="B5" s="34" t="n">
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="C5" s="18" t="str">
